--- a/data/trans_dic/P39A5_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P39A5_2023-Provincia-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que sí diría que estar con dificultad para respirar es un síntoma de que a alguien le está dando un ataque al corazón</t>
+          <t>Población que sí diría que estar con dificultad para respirar es un síntoma de que a alguien le está dando un ataque al corazón (tasa de respuesta: 91,17%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>55,59; 69,13</t>
+          <t>55,52; 69,12</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>57,71; 66,95</t>
+          <t>57,16; 66,71</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>58,08; 66,6</t>
+          <t>58,28; 66,41</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>95,71; 99,15</t>
+          <t>95,48; 99,03</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>94,93; 97,84</t>
+          <t>94,86; 97,78</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>96,11; 98,15</t>
+          <t>95,98; 98,15</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>71,1; 80,74</t>
+          <t>70,64; 81,02</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>66,38; 75,24</t>
+          <t>65,9; 74,83</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>70,21; 76,67</t>
+          <t>70,16; 76,7</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>95,16; 99,16</t>
+          <t>94,95; 99,07</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>42,91; 96,34</t>
+          <t>43,36; 96,36</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>57,57; 97,13</t>
+          <t>57,97; 97,23</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>97,32; 100,0</t>
+          <t>97,24; 100,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>96,03; 100,0</t>
+          <t>95,14; 100,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>97,36; 99,73</t>
+          <t>97,51; 99,73</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>86,03; 93,6</t>
+          <t>86,24; 93,52</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>85,07; 92,22</t>
+          <t>84,89; 91,95</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>86,95; 91,97</t>
+          <t>86,72; 91,87</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>72,61; 80,35</t>
+          <t>72,4; 80,34</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>71,65; 90,54</t>
+          <t>71,64; 90,59</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>73,81; 86,56</t>
+          <t>73,87; 86,78</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>96,0; 99,27</t>
+          <t>96,2; 99,42</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>98,68; 99,7</t>
+          <t>98,72; 99,69</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>97,67; 99,23</t>
+          <t>97,66; 99,25</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>86,56; 91,01</t>
+          <t>86,62; 91,05</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>79,85; 87,91</t>
+          <t>78,47; 87,89</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>83,85; 88,45</t>
+          <t>83,65; 88,57</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que sí diría que estar con dificultad para respirar es un síntoma de que a alguien le está dando un ataque al corazón</t>
+          <t>Población que sí diría que estar con dificultad para respirar es un síntoma de que a alguien le está dando un ataque al corazón (tasa de respuesta: 91,17%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>172739; 214810</t>
+          <t>172512; 214760</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>163720; 189925</t>
+          <t>162143; 189238</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>345229; 395863</t>
+          <t>346438; 394738</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>480112; 497357</t>
+          <t>478940; 496772</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>472614; 487070</t>
+          <t>472244; 486768</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>960562; 980998</t>
+          <t>959263; 980993</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>204766; 232523</t>
+          <t>203454; 233325</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>203317; 230438</t>
+          <t>201834; 229174</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>417265; 455625</t>
+          <t>416950; 455813</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>233599; 243419</t>
+          <t>233085; 243189</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>156270; 350855</t>
+          <t>157909; 350922</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>350960; 592187</t>
+          <t>353423; 592753</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>171133; 175854</t>
+          <t>171009; 175854</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>196720; 204845</t>
+          <t>194883; 204845</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>370645; 379658</t>
+          <t>371224; 379653</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>210373; 228889</t>
+          <t>210890; 228694</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>186886; 202601</t>
+          <t>186500; 202001</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>403643; 426955</t>
+          <t>402567; 426493</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>423742; 468949</t>
+          <t>422523; 468905</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>576063; 727875</t>
+          <t>575967; 728286</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1024190; 1201071</t>
+          <t>1024992; 1204180</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>822998; 851059</t>
+          <t>824702; 852362</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>657782; 664580</t>
+          <t>658024; 664522</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1488444; 1512210</t>
+          <t>1488285; 1512434</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>2776002; 2918806</t>
+          <t>2778139; 2920246</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>2672728; 2942438</t>
+          <t>2626326; 2941614</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>5495729; 5797475</t>
+          <t>5482791; 5805045</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P39A5_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P39A5_2023-Provincia-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>62,68%</t>
+          <t>62,95%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>62,25%</t>
+          <t>62,79%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>62,48%</t>
+          <t>62,87%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>55,52; 69,12</t>
+          <t>57,44; 68,8</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>57,16; 66,71</t>
+          <t>58,46; 67,48</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>58,28; 66,41</t>
+          <t>59,14; 66,22</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,12%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>95,48; 99,03</t>
+          <t>95,65; 98,92</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>94,86; 97,78</t>
+          <t>94,85; 97,76</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>95,98; 98,15</t>
+          <t>95,86; 98,0</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>76,4%</t>
+          <t>75,74%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>71,07%</t>
+          <t>70,51%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>73,65%</t>
+          <t>73,02%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>70,64; 81,02</t>
+          <t>70,23; 80,32</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>65,9; 74,83</t>
+          <t>66,12; 74,87</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>70,16; 76,7</t>
+          <t>69,76; 76,28</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>77,43%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>85,65%</t>
+          <t>95,9%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>94,95; 99,07</t>
+          <t>91,5; 98,66</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>43,36; 96,36</t>
+          <t>93,0; 97,37</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>57,97; 97,23</t>
+          <t>93,26; 97,33</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,46%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>97,24; 100,0</t>
+          <t>97,77; 100,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>95,14; 100,0</t>
+          <t>98,56; 100,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>97,51; 99,73</t>
+          <t>98,67; 99,83</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>90,46%</t>
+          <t>90,13%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>88,9%</t>
+          <t>88,02%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>89,73%</t>
+          <t>89,11%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>86,24; 93,52</t>
+          <t>86,21; 93,22</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>84,89; 91,95</t>
+          <t>83,99; 91,32</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>86,72; 91,87</t>
+          <t>86,24; 91,4</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>76,72%</t>
+          <t>74,95%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>79,59%</t>
+          <t>72,1%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>78,38%</t>
+          <t>73,48%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>72,4; 80,34</t>
+          <t>71,36; 78,93</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>71,64; 90,59</t>
+          <t>68,91; 74,96</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>73,87; 86,78</t>
+          <t>71,0; 76,0</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>97,88%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>96,2; 99,42</t>
+          <t>94,73; 98,07</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>98,72; 99,69</t>
+          <t>97,75; 99,41</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>97,66; 99,25</t>
+          <t>96,83; 98,61</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>88,2%</t>
+          <t>86,82%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>85,37%</t>
+          <t>86,01%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>86,76%</t>
+          <t>86,4%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>86,62; 91,05</t>
+          <t>85,53; 88,14</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>78,47; 87,89</t>
+          <t>84,99; 87,05</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>83,65; 88,57</t>
+          <t>85,56; 87,2</t>
         </is>
       </c>
     </row>
@@ -1111,17 +1111,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>194764</t>
+          <t>200229</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>176606</t>
+          <t>195692</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>371370</t>
+          <t>395921</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>172512; 214760</t>
+          <t>182702; 218827</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>162143; 189238</t>
+          <t>182216; 210309</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>346438; 394738</t>
+          <t>372436; 417039</t>
         </is>
       </c>
     </row>
@@ -1184,17 +1184,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>491312</t>
+          <t>501241</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>480977</t>
+          <t>509732</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>972290</t>
+          <t>1010973</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>478940; 496772</t>
+          <t>490471; 507239</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>472244; 486768</t>
+          <t>500960; 516336</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>959263; 980993</t>
+          <t>997850; 1020063</t>
         </is>
       </c>
     </row>
@@ -1257,17 +1257,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>220025</t>
+          <t>216778</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>217680</t>
+          <t>219841</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>437704</t>
+          <t>436618</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>203454; 233325</t>
+          <t>201005; 229887</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>201834; 229174</t>
+          <t>206156; 233416</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>416950; 455813</t>
+          <t>417133; 456158</t>
         </is>
       </c>
     </row>
@@ -1330,17 +1330,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>240149</t>
+          <t>271831</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>282002</t>
+          <t>313996</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>522152</t>
+          <t>585827</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>233085; 243189</t>
+          <t>258090; 278284</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>157909; 350922</t>
+          <t>305832; 320181</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>353423; 592753</t>
+          <t>569740; 594604</t>
         </is>
       </c>
     </row>
@@ -1403,17 +1403,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>174496</t>
+          <t>199963</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>202902</t>
+          <t>222107</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>377398</t>
+          <t>422071</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>171009; 175854</t>
+          <t>196941; 201426</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>194883; 204845</t>
+          <t>219723; 222938</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>371224; 379653</t>
+          <t>418739; 423649</t>
         </is>
       </c>
     </row>
@@ -1476,17 +1476,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>221209</t>
+          <t>216634</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>195309</t>
+          <t>198215</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>416519</t>
+          <t>414849</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>210890; 228694</t>
+          <t>207203; 224070</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>186500; 202001</t>
+          <t>189145; 205635</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>402567; 426493</t>
+          <t>401474; 425508</t>
         </is>
       </c>
     </row>
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>447749</t>
+          <t>503393</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>639827</t>
+          <t>515365</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1087577</t>
+          <t>1018758</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>422523; 468905</t>
+          <t>479278; 530137</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>575967; 728286</t>
+          <t>492617; 535832</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1024992; 1204180</t>
+          <t>984404; 1053779</t>
         </is>
       </c>
     </row>
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>839075</t>
+          <t>686670</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>662140</t>
+          <t>759562</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1501216</t>
+          <t>1446231</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>824702; 852362</t>
+          <t>671529; 695245</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>658024; 664522</t>
+          <t>751311; 764052</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1488285; 1512434</t>
+          <t>1430707; 1457015</t>
         </is>
       </c>
     </row>
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>2828781</t>
+          <t>2796740</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2857444</t>
+          <t>2934509</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>5686225</t>
+          <t>5731249</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>2778139; 2920246</t>
+          <t>2755388; 2839553</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>2626326; 2941614</t>
+          <t>2899864; 2969986</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>5482791; 5805045</t>
+          <t>5675764; 5784167</t>
         </is>
       </c>
     </row>
